--- a/templates/festivi_template.xlsx
+++ b/templates/festivi_template.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seria\Desktop\Repositories\shifter\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E3E7E13-F387-4B15-8158-A3304E9D837B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B850AF0-A510-4041-8D60-D7C18229157F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26835" windowHeight="12060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26835" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="festivi_NOV" sheetId="1" r:id="rId1"/>
@@ -20,7 +15,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -855,7 +850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -863,11 +858,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>45962</v>
-      </c>
+      <c r="A1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>